--- a/pensum/ok07/LOM_Ovingsark_Okonomistyring_kap07_Knapp_faktor_NY.xlsx
+++ b/pensum/ok07/LOM_Ovingsark_Okonomistyring_kap07_Knapp_faktor_NY.xlsx
@@ -190,7 +190,7 @@
     <t xml:space="preserve">Samme oppsett, tomt. Legg inn dine egne oppdragstyper.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tallene som ligger inne er ordreboka til Nordlys Elektro AS i mars, den samme bedriften du møter i alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Tallene som ligger inne er ordreboka til Nordlys Elektro AS i mars, den samme bedriften du møter i alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Rangeringene regnes med RANK, og planene fylles ovenfra og ned med INDEX og MATCH. Snur du et tall, snur rangeringen og planen med den.</t>
@@ -331,7 +331,7 @@
     <t xml:space="preserve">Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">De fire oppdragstypene</t>
@@ -436,7 +436,7 @@
     <t xml:space="preserve">Prøv dette: sett dekningsbidraget for nybygg i B7 opp til det gir samme beløp per montørtime som ladepunktet. Se hva som skjer med rangeringen — og med planen i arket Produktvalg.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 7.1 og 7.2. Oppdragstypene og tallene er Nordlys Elektro AS' egne.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 7.1 og 7.2. Oppdragstypene og tallene er Nordlys Elektro AS' egne.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvem får montørtimene?</t>
@@ -571,7 +571,7 @@
     <t xml:space="preserve">Prøv dette: sett kapasiteten i B5 opp til det er timer nok til alle forespørslene. Da forsvinner forskjellen mellom de to planene — og det er nettopp poenget: rangeringen betyr bare noe når noe er knapt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 7.2 om dekningsbidrag per enhet av den knappe faktoren.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 7.2 om dekningsbidrag per enhet av den knappe faktoren.</t>
   </si>
   <si>
     <t xml:space="preserve">Når det er materiellet som mangler</t>
@@ -640,7 +640,7 @@
     <t xml:space="preserve">Står det montørtimer ubrukt?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 7.3 om flere knappe faktorer og om produkter som bidrar til salget av andre.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 7.3 om flere knappe faktorer og om produkter som bidrar til salget av andre.</t>
   </si>
   <si>
     <t xml:space="preserve">To rammeavtaler om de samme timene</t>
@@ -769,7 +769,7 @@
     <t xml:space="preserve">Legg merke til forskjellen på de to risikoene: volumet må svikte med over halvparten før valget snur, mens en rabatt på under sju prosent av prisen gjør det. Det er prisen dere skal forhandle om, ikke volumgarantien.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 7.2 og 7.3. Prisen på ladepunktet er Nordlys' egen, den samme som i kapittel 2 om priselastisitet. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 7.2 og 7.3. Prisen på ladepunktet er Nordlys' egen, den samme som i kapittel 2 om priselastisitet. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
     <t xml:space="preserve">Din egen bedrift</t>
